--- a/Results/Methanol economics.xlsx
+++ b/Results/Methanol economics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD44A3C1-41A2-4CFA-B74F-03E4639270E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8BC76B-B0A3-43AF-9E7B-0840254C650E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{741FF5BF-5CBD-4A41-8A6D-60044BC89C80}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{741FF5BF-5CBD-4A41-8A6D-60044BC89C80}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -702,15 +702,15 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(D3:D12)</f>
-        <v>0.18006127907606934</v>
+        <v>0.15126361064573562</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.13052289868226805</v>
+        <v>0.11719122170895088</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>0.25748312288407949</v>
+        <v>0.18533599958252039</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>11</v>
@@ -737,30 +737,29 @@
       </c>
       <c r="D3" s="4">
         <f>$B3*O3</f>
-        <v>7.3373147450400009E-2</v>
+        <v>4.6841402967831812E-2</v>
       </c>
       <c r="E3" s="4">
         <f>$B3*P3</f>
-        <v>3.5754722597999999E-2</v>
+        <v>2.3420701483915906E-2</v>
       </c>
       <c r="F3" s="4">
         <f>$B3*Q3</f>
-        <v>0.13260646692719996</v>
+        <v>7.0262104451747728E-2</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f>144.88/1000*0.777</f>
-        <v>0.11257176000000001</v>
+        <v>7.1865789545454542E-2</v>
       </c>
       <c r="P3" s="4">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>3.5932894772727271E-2</v>
       </c>
       <c r="Q3" s="4">
-        <f>261.84/1000*0.777</f>
-        <v>0.20344967999999997</v>
+        <f>O3*1.5</f>
+        <v>0.10779868431818182</v>
       </c>
       <c r="R3" t="s">
         <v>15</v>
@@ -778,30 +777,29 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D6" si="1">$B4*O4</f>
-        <v>2.1316738853503187E-2</v>
+        <v>1.3607374905737681E-2</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" ref="E4:E6" si="2">$B4*P4</f>
-        <v>1.0387643312101911E-2</v>
+        <v>6.8036874528688406E-3</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" ref="F4:F6" si="3">$B4*Q4</f>
-        <v>3.8525503184713372E-2</v>
+        <v>2.041106235860652E-2</v>
       </c>
       <c r="N4" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="4">
-        <f>144.88/1000/47.1</f>
-        <v>3.0760084925690024E-3</v>
+        <v>1.9635461624441099E-3</v>
       </c>
       <c r="P4" s="4">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="4">O4*0.5</f>
+        <v>9.8177308122205493E-4</v>
       </c>
       <c r="Q4" s="4">
-        <f>261.84/1000/47.1</f>
-        <v>5.5592356687898083E-3</v>
+        <f t="shared" ref="Q4:Q5" si="5">O4*1.5</f>
+        <v>2.9453192436661646E-3</v>
       </c>
       <c r="R4" t="s">
         <v>16</v>
@@ -819,30 +817,29 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="1"/>
-        <v>2.2525599999999998E-3</v>
+        <v>7.6960000000000006E-3</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="2"/>
-        <v>1.2616999999999999E-3</v>
+        <v>3.8480000000000003E-3</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="3"/>
-        <v>3.2323199999999995E-3</v>
+        <v>1.1544000000000002E-2</v>
       </c>
       <c r="N5" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="4">
-        <f>30.44/1000</f>
-        <v>3.0440000000000002E-2</v>
+        <v>0.10400000000000001</v>
       </c>
       <c r="P5" s="4">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="4"/>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="Q5" s="4">
-        <f>43.68/1000</f>
-        <v>4.3679999999999997E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.15600000000000003</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -874,13 +871,13 @@
         <v>21</v>
       </c>
       <c r="O6" s="4">
-        <v>3.2</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="P6" s="4">
-        <v>2.7</v>
+        <v>8.34</v>
       </c>
       <c r="Q6" s="4">
-        <v>4</v>
+        <v>15.9</v>
       </c>
       <c r="R6" t="s">
         <v>14</v>
@@ -897,28 +894,28 @@
         <v>3</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" ref="D7" si="4">$B7*O7</f>
+        <f t="shared" ref="D7" si="6">$B7*O7</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" ref="E7" si="5">$B7*P7</f>
+        <f t="shared" ref="E7" si="7">$B7*P7</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f t="shared" ref="F7" si="6">$B7*Q7</f>
+        <f t="shared" ref="F7" si="8">$B7*Q7</f>
         <v>0</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
       </c>
       <c r="O7" s="4">
-        <v>3</v>
+        <v>6.88</v>
       </c>
       <c r="P7" s="4">
-        <v>2.2000000000000002</v>
+        <v>5.23</v>
       </c>
       <c r="Q7" s="4">
-        <v>4</v>
+        <v>8.48</v>
       </c>
       <c r="R7" t="s">
         <v>14</v>
@@ -935,31 +932,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:F10" si="7">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="9">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>48</v>
       </c>
       <c r="O8" s="4">
-        <f>453/1000</f>
-        <v>0.45300000000000001</v>
+        <v>0.36153846153846153</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" ref="P8:Q8" si="8">453/1000</f>
-        <v>0.45300000000000001</v>
+        <v>0.26923076923076922</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="8"/>
-        <v>0.45300000000000001</v>
+        <v>0.62307692307692308</v>
       </c>
       <c r="R8" t="s">
         <v>14</v>
@@ -976,15 +970,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -1014,15 +1008,15 @@
         <v>3</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -1159,15 +1153,15 @@
       </c>
       <c r="D15" s="4">
         <f>SUM(D16:D25)</f>
-        <v>0.18502299907606934</v>
+        <v>0.16821561064573565</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" ref="E15" si="9">SUM(E16:E25)</f>
-        <v>0.13330204868226805</v>
+        <f t="shared" ref="E15" si="10">SUM(E16:E25)</f>
+        <v>0.12566722170895089</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" ref="F15" si="10">SUM(F16:F25)</f>
-        <v>0.26460296288407947</v>
+        <f t="shared" ref="F15" si="11">SUM(F16:F25)</f>
+        <v>0.2107639995825204</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1185,16 +1179,16 @@
         <v>4</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16:F23" si="11">$B16*O3</f>
-        <v>7.3373147450400009E-2</v>
+        <f t="shared" ref="D16:F23" si="12">$B16*O3</f>
+        <v>4.6841402967831812E-2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="11"/>
-        <v>3.5754722597999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.3420701483915906E-2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="11"/>
-        <v>0.13260646692719996</v>
+        <f t="shared" si="12"/>
+        <v>7.0262104451747728E-2</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
@@ -1215,16 +1209,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="11"/>
-        <v>2.1316738853503187E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.3607374905737681E-2</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="11"/>
-        <v>1.0387643312101911E-2</v>
+        <f t="shared" si="12"/>
+        <v>6.8036874528688406E-3</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="11"/>
-        <v>3.8525503184713372E-2</v>
+        <f t="shared" si="12"/>
+        <v>2.041106235860652E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>7</v>
@@ -1254,16 +1248,16 @@
         <v>5</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="11"/>
-        <v>7.21428E-3</v>
+        <f t="shared" si="12"/>
+        <v>2.4648E-2</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="11"/>
-        <v>4.0408499999999995E-3</v>
+        <f t="shared" si="12"/>
+        <v>1.2324E-2</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="11"/>
-        <v>1.0352159999999999E-2</v>
+        <f t="shared" si="12"/>
+        <v>3.6972000000000005E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>8</v>
@@ -1293,15 +1287,15 @@
         <v>3</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1316,15 +1310,15 @@
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1339,15 +1333,15 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1362,15 +1356,15 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1385,15 +1379,15 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -1416,7 +1410,7 @@
         <v>5.4958353909465019E-2</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:F25" si="12">E24</f>
+        <f t="shared" ref="F24:F25" si="13">E24</f>
         <v>5.4958353909465019E-2</v>
       </c>
     </row>
@@ -1435,11 +1429,11 @@
         <v>2.8160478862701125E-2</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="13">D25</f>
+        <f t="shared" ref="E25" si="14">D25</f>
         <v>2.8160478862701125E-2</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.8160478862701125E-2</v>
       </c>
     </row>
@@ -1482,15 +1476,15 @@
       </c>
       <c r="D28" s="4">
         <f>SUM(D29:D38)</f>
-        <v>1.3562557979697929</v>
+        <v>2.0605605915281244</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28" si="14">SUM(E29:E38)</f>
-        <v>1.2827122790388357</v>
+        <f t="shared" ref="E28" si="15">SUM(E29:E38)</f>
+        <v>1.7664725325937414</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" ref="F28" si="15">SUM(F29:F38)</f>
-        <v>1.4714465329363848</v>
+        <f t="shared" ref="F28" si="16">SUM(F29:F38)</f>
+        <v>3.446778169050817</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
@@ -1507,15 +1501,15 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" ref="D29:F36" si="16">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="17">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O29" s="4"/>
@@ -1533,15 +1527,15 @@
         <v>6</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -1556,16 +1550,16 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="16"/>
-        <v>9.2201336302895204E-3</v>
+        <f t="shared" si="17"/>
+        <v>3.1501113585746067E-2</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="16"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="17"/>
+        <v>1.5750556792873033E-2</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="16"/>
-        <v>1.3230467706013346E-2</v>
+        <f t="shared" si="17"/>
+        <v>4.7251670378619104E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -1579,16 +1573,16 @@
         <v>3</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="16"/>
-        <v>0.44472160356347201</v>
+        <f t="shared" si="17"/>
+        <v>1.2813541202672538</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="16"/>
-        <v>0.37523385300667955</v>
+        <f t="shared" si="17"/>
+        <v>1.1590556792872988</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="16"/>
-        <v>0.55590200445434002</v>
+        <f t="shared" si="17"/>
+        <v>2.2097104677060018</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -1602,15 +1596,15 @@
         <v>3</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -1625,16 +1619,16 @@
         <v>3</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="16"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="17"/>
+        <v>0.61115298954942288</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="16"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="17"/>
+        <v>0.45511392838786807</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="16"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="17"/>
+        <v>1.0532636628404948</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -1648,15 +1642,15 @@
         <v>3</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -1671,15 +1665,15 @@
         <v>3</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -1702,7 +1696,7 @@
         <v>9.0288724279835392E-2</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F38" si="17">E37</f>
+        <f t="shared" ref="F37:F38" si="18">E37</f>
         <v>9.0288724279835392E-2</v>
       </c>
       <c r="N37" s="6"/>
@@ -1726,11 +1720,11 @@
         <v>4.6263643845866072E-2</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="18">D38</f>
+        <f t="shared" ref="E38" si="19">D38</f>
         <v>4.6263643845866072E-2</v>
       </c>
       <c r="F38" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4.6263643845866072E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -1774,15 +1768,15 @@
       </c>
       <c r="D41" s="4">
         <f>SUM(D42:D51)</f>
-        <v>1.3284606977470759</v>
+        <v>1.7353579189223352</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41" si="19">SUM(E42:E51)</f>
-        <v>1.2132245284820433</v>
+        <f t="shared" ref="E41" si="20">SUM(E42:E51)</f>
+        <v>1.3342587241304922</v>
       </c>
       <c r="F41" s="4">
-        <f t="shared" ref="F41" si="20">SUM(F42:F51)</f>
-        <v>1.4714465329363848</v>
+        <f t="shared" ref="F41" si="21">SUM(F42:F51)</f>
+        <v>2.4155799507880165</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -1796,15 +1790,15 @@
         <v>4</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" ref="D42:F49" si="21">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="22">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -1819,15 +1813,15 @@
         <v>6</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F43" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -1842,16 +1836,16 @@
         <v>5</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="21"/>
-        <v>9.2201336302895204E-3</v>
+        <f t="shared" si="22"/>
+        <v>3.1501113585746067E-2</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="21"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="22"/>
+        <v>1.5750556792873033E-2</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="21"/>
-        <v>1.3230467706013346E-2</v>
+        <f t="shared" si="22"/>
+        <v>4.7251670378619104E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -1865,15 +1859,15 @@
         <v>3</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F45" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -1888,16 +1882,16 @@
         <v>3</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="21"/>
-        <v>0.41692650334075498</v>
+        <f t="shared" si="22"/>
+        <v>0.95615144766146476</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="21"/>
-        <v>0.30574610244988704</v>
+        <f t="shared" si="22"/>
+        <v>0.72684187082404961</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" si="21"/>
-        <v>0.55590200445434002</v>
+        <f t="shared" si="22"/>
+        <v>1.178512249443201</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -1911,16 +1905,16 @@
         <v>3</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="21"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="22"/>
+        <v>0.61115298954942288</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="21"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="22"/>
+        <v>0.45511392838786807</v>
       </c>
       <c r="F47" s="4">
-        <f t="shared" si="21"/>
-        <v>0.76576169265033001</v>
+        <f t="shared" si="22"/>
+        <v>1.0532636628404948</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -1934,15 +1928,15 @@
         <v>3</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -1957,15 +1951,15 @@
         <v>3</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -1988,7 +1982,7 @@
         <v>9.0288724279835392E-2</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:F51" si="22">E50</f>
+        <f t="shared" ref="F50:F51" si="23">E50</f>
         <v>9.0288724279835392E-2</v>
       </c>
     </row>
@@ -2007,11 +2001,11 @@
         <v>4.6263643845866072E-2</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="23">D51</f>
+        <f t="shared" ref="E51" si="24">D51</f>
         <v>4.6263643845866072E-2</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.6263643845866072E-2</v>
       </c>
     </row>
@@ -2081,15 +2075,15 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(D3:D12)</f>
-        <v>0.55571129600403091</v>
+        <v>0.19512765857011663</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.13737401525426576</v>
+        <v>0.14254880395714026</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>2.1700700581164454</v>
+        <v>0.24770651318309297</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>11</v>
@@ -2116,30 +2110,29 @@
       </c>
       <c r="D3" s="4">
         <f>$B3*O3</f>
-        <v>0.35532395073630008</v>
+        <v>7.5579848266936367E-2</v>
       </c>
       <c r="E3" s="4">
         <f>$B3*P3</f>
-        <v>3.5754722597999999E-2</v>
+        <v>3.7789924133468183E-2</v>
       </c>
       <c r="F3" s="4">
         <f>$B3*Q3</f>
-        <v>1.5849116418933</v>
+        <v>0.11336977240040454</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
+        <v>0.11595736090909091</v>
       </c>
       <c r="P3" s="4">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>5.7978680454545455E-2</v>
       </c>
       <c r="Q3" s="4">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
+        <f>O3*1.5</f>
+        <v>0.17393604136363636</v>
       </c>
       <c r="R3" t="s">
         <v>15</v>
@@ -2157,30 +2150,29 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.10323051592356688</v>
+        <v>2.1955860959016391E-2</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="1"/>
-        <v>1.0387643312101911E-2</v>
+        <v>1.0977930479508196E-2</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
-        <v>0.4604565668789809</v>
+        <v>3.2933791438524582E-2</v>
       </c>
       <c r="N4" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="4">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
+        <v>3.16823390461997E-3</v>
       </c>
       <c r="P4" s="4">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.584116952309985E-3</v>
       </c>
       <c r="Q4" s="4">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>4.7523508569299548E-3</v>
       </c>
       <c r="R4" t="s">
         <v>16</v>
@@ -2198,30 +2190,29 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="1"/>
-        <v>7.1868799999999997E-3</v>
+        <v>7.6220000000000003E-3</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="1"/>
-        <v>1.2616999999999999E-3</v>
+        <v>3.8110000000000002E-3</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>3.4731900000000003E-2</v>
+        <v>1.1433000000000002E-2</v>
       </c>
       <c r="N5" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="4">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
+        <v>0.10300000000000001</v>
       </c>
       <c r="P5" s="4">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.1500000000000004E-2</v>
       </c>
       <c r="Q5" s="4">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
+        <f t="shared" si="3"/>
+        <v>0.15450000000000003</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -2253,13 +2244,13 @@
         <v>21</v>
       </c>
       <c r="O6" s="4">
-        <v>2.5</v>
+        <v>6.67</v>
       </c>
       <c r="P6" s="4">
-        <v>1.8</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="Q6" s="4">
-        <v>2.7</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="R6" t="s">
         <v>14</v>
@@ -2291,13 +2282,13 @@
         <v>22</v>
       </c>
       <c r="O7" s="4">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="P7" s="4">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R7" t="s">
         <v>14</v>
@@ -2314,31 +2305,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="4">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>48</v>
       </c>
       <c r="O8" s="4">
-        <f>373.599/1000</f>
-        <v>0.37359900000000001</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" ref="P8:Q8" si="3">373.599/1000</f>
-        <v>0.37359900000000001</v>
+        <v>0.12307692307692308</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="3"/>
-        <v>0.37359900000000001</v>
+        <v>0.46923076923076923</v>
       </c>
       <c r="R8" t="s">
         <v>14</v>
@@ -2355,15 +2343,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -2393,15 +2381,15 @@
         <v>3</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -2539,15 +2527,15 @@
       </c>
       <c r="D15" s="4">
         <f>SUM(D16:D25)</f>
-        <v>0.57154185600403085</v>
+        <v>0.21191665857011663</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" ref="E15:F15" si="4">SUM(E16:E25)</f>
-        <v>0.14015316525426577</v>
+        <f t="shared" ref="E15:F15" si="5">SUM(E16:E25)</f>
+        <v>0.15094330395714026</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="4"/>
-        <v>2.2465741081164454</v>
+        <f t="shared" si="5"/>
+        <v>0.27289001318309297</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -2565,16 +2553,16 @@
         <v>4</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16:F23" si="5">$B16*O3</f>
-        <v>0.35532395073630008</v>
+        <f t="shared" ref="D16:F23" si="6">$B16*O3</f>
+        <v>7.5579848266936367E-2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>3.5754722597999999E-2</v>
+        <f t="shared" si="6"/>
+        <v>3.7789924133468183E-2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="5"/>
-        <v>1.5849116418933</v>
+        <f t="shared" si="6"/>
+        <v>0.11336977240040454</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
@@ -2595,16 +2583,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.10323051592356688</v>
+        <f t="shared" si="6"/>
+        <v>2.1955860959016391E-2</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="5"/>
-        <v>1.0387643312101911E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.0977930479508196E-2</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.4604565668789809</v>
+        <f t="shared" si="6"/>
+        <v>3.2933791438524582E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>7</v>
@@ -2634,16 +2622,16 @@
         <v>5</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.301744E-2</v>
+        <f t="shared" si="6"/>
+        <v>2.4411000000000002E-2</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="5"/>
-        <v>4.0408499999999995E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.2205500000000001E-2</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="5"/>
-        <v>0.11123595</v>
+        <f t="shared" si="6"/>
+        <v>3.6616500000000003E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>8</v>
@@ -2673,15 +2661,15 @@
         <v>3</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2696,15 +2684,15 @@
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2719,15 +2707,15 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2742,15 +2730,15 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2765,15 +2753,15 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2796,7 +2784,7 @@
         <v>5.9488327161988104E-2</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:F25" si="6">E24</f>
+        <f t="shared" ref="F24:F25" si="7">E24</f>
         <v>5.9488327161988104E-2</v>
       </c>
     </row>
@@ -2815,11 +2803,11 @@
         <v>3.0481622182175767E-2</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="7">D25</f>
+        <f t="shared" ref="E25" si="8">D25</f>
         <v>3.0481622182175767E-2</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0481622182175767E-2</v>
       </c>
     </row>
@@ -2862,15 +2850,15 @@
       </c>
       <c r="D28" s="4">
         <f>SUM(D29:D38)</f>
-        <v>1.1562041235884741</v>
+        <v>1.4310539620328788</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28:F28" si="8">SUM(E29:E38)</f>
-        <v>1.0346684443011696</v>
+        <f t="shared" ref="E28:F28" si="9">SUM(E29:E38)</f>
+        <v>0.93569949912385264</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="8"/>
-        <v>1.2967459498690974</v>
+        <f t="shared" si="9"/>
+        <v>2.2774963125554031</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
@@ -2887,15 +2875,15 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" ref="D29:F36" si="9">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="10">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O29" s="4"/>
@@ -2913,15 +2901,15 @@
         <v>6</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -2936,16 +2924,16 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="9"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="10"/>
+        <v>3.11982182628062E-2</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="9"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.55991091314031E-2</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="9"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="10"/>
+        <v>4.6797327394209304E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -2959,16 +2947,16 @@
         <v>3</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.34743875278396252</v>
+        <f t="shared" si="10"/>
+        <v>0.92696659242761192</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.25015590200445303</v>
+        <f t="shared" si="10"/>
+        <v>0.56424053452115508</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.37523385300667955</v>
+        <f t="shared" si="10"/>
+        <v>1.2896926503340687</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -2982,15 +2970,15 @@
         <v>3</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3005,16 +2993,16 @@
         <v>3</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="10"/>
+        <v>0.32508137741990578</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="10"/>
+        <v>0.20805208154873969</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="10"/>
+        <v>0.79319856090457008</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -3028,15 +3016,15 @@
         <v>3</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3051,15 +3039,15 @@
         <v>3</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -3082,7 +3070,7 @@
         <v>9.7730823194694755E-2</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F38" si="10">E37</f>
+        <f t="shared" ref="F37:F38" si="11">E37</f>
         <v>9.7730823194694755E-2</v>
       </c>
       <c r="N37" s="6"/>
@@ -3106,11 +3094,11 @@
         <v>5.0076950727860121E-2</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="11">D38</f>
+        <f t="shared" ref="E38" si="12">D38</f>
         <v>5.0076950727860121E-2</v>
       </c>
       <c r="F38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.0076950727860121E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -3154,15 +3142,15 @@
       </c>
       <c r="D41" s="4">
         <f>SUM(D42:D51)</f>
-        <v>1.1562041235884741</v>
+        <v>1.3031965010083808</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41:F41" si="12">SUM(E42:E51)</f>
-        <v>1.0346684443011696</v>
+        <f t="shared" ref="E41:F41" si="13">SUM(E42:E51)</f>
+        <v>0.85787321850024512</v>
       </c>
       <c r="F41" s="4">
-        <f t="shared" si="12"/>
-        <v>1.3384386002031727</v>
+        <f t="shared" si="13"/>
+        <v>2.0996076711300145</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -3176,15 +3164,15 @@
         <v>4</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" ref="D42:F49" si="13">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="14">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3199,15 +3187,15 @@
         <v>6</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3222,16 +3210,16 @@
         <v>5</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="13"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.11982182628062E-2</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="13"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.55991091314031E-2</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="13"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="14"/>
+        <v>4.6797327394209304E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -3245,15 +3233,15 @@
         <v>3</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3268,16 +3256,16 @@
         <v>3</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.34743875278396252</v>
+        <f t="shared" si="14"/>
+        <v>0.79910913140311379</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.25015590200445303</v>
+        <f t="shared" si="14"/>
+        <v>0.4864142538975475</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.41692650334075498</v>
+        <f t="shared" si="14"/>
+        <v>1.11180400890868</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -3291,16 +3279,16 @@
         <v>3</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="14"/>
+        <v>0.32508137741990578</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="14"/>
+        <v>0.20805208154873969</v>
       </c>
       <c r="F47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.63154040311803683</v>
+        <f t="shared" si="14"/>
+        <v>0.79319856090457008</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -3314,15 +3302,15 @@
         <v>3</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3337,15 +3325,15 @@
         <v>3</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -3368,7 +3356,7 @@
         <v>9.7730823194694755E-2</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:F51" si="14">E50</f>
+        <f t="shared" ref="F50:F51" si="15">E50</f>
         <v>9.7730823194694755E-2</v>
       </c>
     </row>
@@ -3387,11 +3375,11 @@
         <v>5.0076950727860121E-2</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="15">D51</f>
+        <f t="shared" ref="E51" si="16">D51</f>
         <v>5.0076950727860121E-2</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.0076950727860121E-2</v>
       </c>
     </row>
@@ -3460,15 +3448,15 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(D3:D12)</f>
-        <v>0.5631271197154053</v>
+        <v>0.2085279669933025</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.14478983896564024</v>
+        <v>0.15295687002442038</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>2.1774858818278195</v>
+        <v>0.26409906396218458</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>11</v>
@@ -3495,30 +3483,29 @@
       </c>
       <c r="D3" s="4">
         <f>$B3*O3</f>
-        <v>0.35532395073630008</v>
+        <v>8.0331874654977264E-2</v>
       </c>
       <c r="E3" s="4">
         <f>$B3*P3</f>
-        <v>3.5754722597999999E-2</v>
+        <v>4.0165937327488632E-2</v>
       </c>
       <c r="F3" s="4">
         <f>$B3*Q3</f>
-        <v>1.5849116418933</v>
+        <v>0.1204978119824659</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
+        <v>0.12324809318181817</v>
       </c>
       <c r="P3" s="4">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>6.1624046590909087E-2</v>
       </c>
       <c r="Q3" s="4">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
+        <f>O3*1.5</f>
+        <v>0.18487213977272726</v>
       </c>
       <c r="R3" t="s">
         <v>15</v>
@@ -3536,30 +3523,29 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.10323051592356688</v>
+        <v>2.3336319282786903E-2</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="1"/>
-        <v>1.0387643312101911E-2</v>
+        <v>1.1668159641393451E-2</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
-        <v>0.4604565668789809</v>
+        <v>3.5004478924180356E-2</v>
       </c>
       <c r="N4" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="4">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
+        <v>3.3674342399403899E-3</v>
       </c>
       <c r="P4" s="4">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.683717119970195E-3</v>
       </c>
       <c r="Q4" s="4">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>5.0511513599105851E-3</v>
       </c>
       <c r="R4" t="s">
         <v>16</v>
@@ -3577,30 +3563,29 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="1"/>
-        <v>7.1868799999999997E-3</v>
+        <v>7.4739999999999989E-3</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="1"/>
-        <v>1.2616999999999999E-3</v>
+        <v>3.7369999999999994E-3</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>3.4731900000000003E-2</v>
+        <v>1.1210999999999999E-2</v>
       </c>
       <c r="N5" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="4">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
+        <v>0.10099999999999999</v>
       </c>
       <c r="P5" s="4">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.0499999999999996E-2</v>
       </c>
       <c r="Q5" s="4">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
+        <f t="shared" si="3"/>
+        <v>0.1515</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -3632,13 +3617,13 @@
         <v>21</v>
       </c>
       <c r="O6" s="4">
-        <v>1.8</v>
+        <v>5.28</v>
       </c>
       <c r="P6" s="4">
-        <v>1.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q6" s="4">
-        <v>2.2000000000000002</v>
+        <v>7.32</v>
       </c>
       <c r="R6" t="s">
         <v>14</v>
@@ -3670,13 +3655,13 @@
         <v>22</v>
       </c>
       <c r="O7" s="4">
-        <v>2</v>
+        <v>4.95</v>
       </c>
       <c r="P7" s="4">
-        <v>1.6</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="Q7" s="4">
-        <v>2.6</v>
+        <v>6.8630000000000004</v>
       </c>
       <c r="R7" t="s">
         <v>14</v>
@@ -3693,31 +3678,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="4">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>48</v>
       </c>
       <c r="O8" s="4">
-        <f>293.931999999999/1000</f>
-        <v>0.29393199999999897</v>
+        <v>0.15769230769230769</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" ref="P8:Q8" si="3">293.931999999999/1000</f>
-        <v>0.29393199999999897</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="3"/>
-        <v>0.29393199999999897</v>
+        <v>0.43076923076923079</v>
       </c>
       <c r="R8" t="s">
         <v>14</v>
@@ -3734,15 +3716,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -3772,15 +3754,15 @@
         <v>3</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -3918,15 +3900,15 @@
       </c>
       <c r="D15" s="4">
         <f>SUM(D16:D25)</f>
-        <v>0.57895767971540535</v>
+        <v>0.22499096699330245</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" ref="E15:F15" si="4">SUM(E16:E25)</f>
-        <v>0.14756898896564025</v>
+        <f t="shared" ref="E15:F15" si="5">SUM(E16:E25)</f>
+        <v>0.16118837002442038</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="4"/>
-        <v>2.2539899318278196</v>
+        <f t="shared" si="5"/>
+        <v>0.28879356396218459</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -3944,16 +3926,16 @@
         <v>4</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16:F23" si="5">$B16*O3</f>
-        <v>0.35532395073630008</v>
+        <f t="shared" ref="D16:F23" si="6">$B16*O3</f>
+        <v>8.0331874654977264E-2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>3.5754722597999999E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.0165937327488632E-2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="5"/>
-        <v>1.5849116418933</v>
+        <f t="shared" si="6"/>
+        <v>0.1204978119824659</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
@@ -3974,16 +3956,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.10323051592356688</v>
+        <f t="shared" si="6"/>
+        <v>2.3336319282786903E-2</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="5"/>
-        <v>1.0387643312101911E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.1668159641393451E-2</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.4604565668789809</v>
+        <f t="shared" si="6"/>
+        <v>3.5004478924180356E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>7</v>
@@ -4013,16 +3995,16 @@
         <v>5</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.301744E-2</v>
+        <f t="shared" si="6"/>
+        <v>2.3936999999999996E-2</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="5"/>
-        <v>4.0408499999999995E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.1968499999999998E-2</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="5"/>
-        <v>0.11123595</v>
+        <f t="shared" si="6"/>
+        <v>3.59055E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>8</v>
@@ -4052,15 +4034,15 @@
         <v>3</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4075,15 +4057,15 @@
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O20" s="4"/>
@@ -4099,15 +4081,15 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O21" s="4"/>
@@ -4123,15 +4105,15 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="4"/>
@@ -4147,15 +4129,15 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O23" s="4"/>
@@ -4179,7 +4161,7 @@
         <v>6.4391686009399624E-2</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:F25" si="6">E24</f>
+        <f t="shared" ref="F24:F25" si="7">E24</f>
         <v>6.4391686009399624E-2</v>
       </c>
       <c r="O24" s="4"/>
@@ -4199,11 +4181,11 @@
         <v>3.2994087046138695E-2</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="7">D25</f>
+        <f t="shared" ref="E25" si="8">D25</f>
         <v>3.2994087046138695E-2</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.2994087046138695E-2</v>
       </c>
     </row>
@@ -4246,15 +4228,15 @@
       </c>
       <c r="D28" s="4">
         <f>SUM(D29:D38)</f>
-        <v>0.9364334696698231</v>
+        <v>1.1909407158579339</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28:F28" si="8">SUM(E29:E38)</f>
-        <v>0.85659044071659385</v>
+        <f t="shared" ref="E28:F28" si="9">SUM(E29:E38)</f>
+        <v>0.80761332164858168</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="8"/>
-        <v>1.1047703961731636</v>
+        <f t="shared" si="9"/>
+        <v>1.9513625078743768</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
@@ -4271,15 +4253,15 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" ref="D29:F36" si="9">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="10">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O29" s="4"/>
@@ -4297,15 +4279,15 @@
         <v>6</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4320,16 +4302,16 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="9"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="10"/>
+        <v>3.0592427616926463E-2</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="9"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.5296213808463232E-2</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="9"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="10"/>
+        <v>4.5888641425389697E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -4343,16 +4325,16 @@
         <v>3</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.25015590200445303</v>
+        <f t="shared" si="10"/>
+        <v>0.73379064587972886</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.19456570155901901</v>
+        <f t="shared" si="10"/>
+        <v>0.45028062360801546</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.30574610244988704</v>
+        <f t="shared" si="10"/>
+        <v>1.0173006681514423</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -4366,15 +4348,15 @@
         <v>3</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4389,16 +4371,16 @@
         <v>3</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="10"/>
+        <v>0.2665667294843227</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="10"/>
+        <v>0.18204557135514723</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="10"/>
+        <v>0.72818228542058894</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -4412,15 +4394,15 @@
         <v>3</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4435,15 +4417,15 @@
         <v>3</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -4466,7 +4448,7 @@
         <v>0.10578634130115654</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F38" si="10">E37</f>
+        <f t="shared" ref="F37:F38" si="11">E37</f>
         <v>0.10578634130115654</v>
       </c>
       <c r="N37" s="6"/>
@@ -4490,11 +4472,11 @@
         <v>5.4204571575799221E-2</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="11">D38</f>
+        <f t="shared" ref="E38" si="12">D38</f>
         <v>5.4204571575799221E-2</v>
       </c>
       <c r="F38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.4204571575799221E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -4538,15 +4520,15 @@
       </c>
       <c r="D41" s="4">
         <f>SUM(D42:D51)</f>
-        <v>0.96422856989253991</v>
+        <v>1.1450788004904509</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41:F41" si="12">SUM(E42:E51)</f>
-        <v>0.88438554093931088</v>
+        <f t="shared" ref="E41:F41" si="13">SUM(E42:E51)</f>
+        <v>0.77954027042363738</v>
       </c>
       <c r="F41" s="4">
-        <f t="shared" si="12"/>
-        <v>1.1603605966185975</v>
+        <f t="shared" si="13"/>
+        <v>1.8878507038654684</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -4560,15 +4542,15 @@
         <v>4</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" ref="D42:F49" si="13">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="14">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4583,15 +4565,15 @@
         <v>6</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4606,16 +4588,16 @@
         <v>5</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="13"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.0592427616926463E-2</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="13"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.5296213808463232E-2</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="13"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="14"/>
+        <v>4.5888641425389697E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -4629,15 +4611,15 @@
         <v>3</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4652,16 +4634,16 @@
         <v>3</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.27795100222717001</v>
+        <f t="shared" si="14"/>
+        <v>0.68792873051224579</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22236080178173601</v>
+        <f t="shared" si="14"/>
+        <v>0.42220757238307122</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.36133630289532104</v>
+        <f t="shared" si="14"/>
+        <v>0.95378886414253394</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -4675,16 +4657,16 @@
         <v>3</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="14"/>
+        <v>0.2665667294843227</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="14"/>
+        <v>0.18204557135514723</v>
       </c>
       <c r="F47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.49686946102449453</v>
+        <f t="shared" si="14"/>
+        <v>0.72818228542058894</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -4698,15 +4680,15 @@
         <v>3</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4721,15 +4703,15 @@
         <v>3</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4752,7 +4734,7 @@
         <v>0.10578634130115654</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:F51" si="14">E50</f>
+        <f t="shared" ref="F50:F51" si="15">E50</f>
         <v>0.10578634130115654</v>
       </c>
     </row>
@@ -4771,11 +4753,11 @@
         <v>5.4204571575799221E-2</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="15">D51</f>
+        <f t="shared" ref="E51" si="16">D51</f>
         <v>5.4204571575799221E-2</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.4204571575799221E-2</v>
       </c>
     </row>
@@ -4844,15 +4826,15 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(D3:D12)</f>
-        <v>0.57115419686994673</v>
+        <v>0.22027336728905156</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ref="E2:F2" si="0">SUM(E3:E12)</f>
-        <v>0.15281691612018172</v>
+        <v>0.1628431087495657</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>2.1855129589823612</v>
+        <v>0.27770362582853741</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>11</v>
@@ -4879,30 +4861,29 @@
       </c>
       <c r="D3" s="4">
         <f>$B3*O3</f>
-        <v>0.35532395073630008</v>
+        <v>8.3499892247004548E-2</v>
       </c>
       <c r="E3" s="4">
         <f>$B3*P3</f>
-        <v>3.5754722597999999E-2</v>
+        <v>4.1749946123502274E-2</v>
       </c>
       <c r="F3" s="4">
         <f>$B3*Q3</f>
-        <v>1.5849116418933</v>
+        <v>0.12524983837050682</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
       <c r="O3" s="4">
-        <f>701.61/1000*0.777</f>
-        <v>0.54515097000000012</v>
+        <v>0.12810858136363637</v>
       </c>
       <c r="P3" s="4">
-        <f>70.6/1000*0.777</f>
-        <v>5.4856200000000001E-2</v>
+        <f>O3*0.5</f>
+        <v>6.4054290681818185E-2</v>
       </c>
       <c r="Q3" s="4">
-        <f>3129.51/1000*0.777</f>
-        <v>2.4316292700000002</v>
+        <f>O3*1.5</f>
+        <v>0.19216287204545457</v>
       </c>
       <c r="R3" t="s">
         <v>15</v>
@@ -4920,30 +4901,29 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:F7" si="1">$B4*O4</f>
-        <v>0.10323051592356688</v>
+        <v>2.4256624831967197E-2</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="1"/>
-        <v>1.0387643312101911E-2</v>
+        <v>1.2128312415983599E-2</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="1"/>
-        <v>0.4604565668789809</v>
+        <v>3.6384937247950798E-2</v>
       </c>
       <c r="N4" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="4">
-        <f>701.61/1000/47.1</f>
-        <v>1.4896178343949046E-2</v>
+        <v>3.5002344634873302E-3</v>
       </c>
       <c r="P4" s="4">
-        <f>70.6/1000/47.1</f>
-        <v>1.4989384288747346E-3</v>
+        <f t="shared" ref="P4:P5" si="2">O4*0.5</f>
+        <v>1.7501172317436651E-3</v>
       </c>
       <c r="Q4" s="4">
-        <f>3129.51/1000/47.1</f>
-        <v>6.644394904458599E-2</v>
+        <f t="shared" ref="Q4:Q5" si="3">O4*1.5</f>
+        <v>5.2503516952309955E-3</v>
       </c>
       <c r="R4" t="s">
         <v>16</v>
@@ -4961,30 +4941,29 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="1"/>
-        <v>7.1868799999999997E-3</v>
+        <v>7.1040000000000001E-3</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="1"/>
-        <v>1.2616999999999999E-3</v>
+        <v>3.552E-3</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="1"/>
-        <v>3.4731900000000003E-2</v>
+        <v>1.0656000000000001E-2</v>
       </c>
       <c r="N5" t="s">
         <v>2</v>
       </c>
       <c r="O5" s="4">
-        <f>97.12/1000</f>
-        <v>9.7119999999999998E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="P5" s="4">
-        <f>17.05/1000</f>
-        <v>1.7049999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="Q5" s="4">
-        <f>469.35/1000</f>
-        <v>0.46935000000000004</v>
+        <f t="shared" si="3"/>
+        <v>0.14400000000000002</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
@@ -5016,13 +4995,13 @@
         <v>21</v>
       </c>
       <c r="O6" s="4">
-        <v>1.5</v>
+        <v>3.927</v>
       </c>
       <c r="P6" s="4">
-        <v>1</v>
+        <v>2.5329999999999999</v>
       </c>
       <c r="Q6" s="4">
-        <v>1.8</v>
+        <v>5.32</v>
       </c>
       <c r="R6" t="s">
         <v>14</v>
@@ -5054,13 +5033,13 @@
         <v>22</v>
       </c>
       <c r="O7" s="4">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="P7" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" s="4">
-        <v>2.2000000000000002</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="R7" t="s">
         <v>14</v>
@@ -5077,31 +5056,28 @@
         <v>3</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:F10" si="2">$B8*O8</f>
+        <f t="shared" ref="D8:F10" si="4">$B8*O8</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N8" t="s">
         <v>48</v>
       </c>
       <c r="O8" s="4">
-        <f>214/1000</f>
-        <v>0.214</v>
+        <v>0.12307692307692308</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" ref="P8:Q8" si="3">214/1000</f>
-        <v>0.214</v>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" si="3"/>
-        <v>0.214</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="R8" t="s">
         <v>14</v>
@@ -5118,15 +5094,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N9" t="s">
@@ -5156,15 +5132,15 @@
         <v>3</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N10" t="s">
@@ -5302,15 +5278,15 @@
       </c>
       <c r="D15" s="4">
         <f>SUM(D16:D25)</f>
-        <v>0.58698475686994678</v>
+        <v>0.23592136728905155</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" ref="E15:F15" si="4">SUM(E16:E25)</f>
-        <v>0.15559606612018173</v>
+        <f t="shared" ref="E15:F15" si="5">SUM(E16:E25)</f>
+        <v>0.1706671087495657</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="4"/>
-        <v>2.2620170089823612</v>
+        <f t="shared" si="5"/>
+        <v>0.30117562582853746</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -5328,16 +5304,16 @@
         <v>4</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16:F23" si="5">$B16*O3</f>
-        <v>0.35532395073630008</v>
+        <f t="shared" ref="D16:F23" si="6">$B16*O3</f>
+        <v>8.3499892247004548E-2</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>3.5754722597999999E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.1749946123502274E-2</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="5"/>
-        <v>1.5849116418933</v>
+        <f t="shared" si="6"/>
+        <v>0.12524983837050682</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
@@ -5358,16 +5334,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.10323051592356688</v>
+        <f t="shared" si="6"/>
+        <v>2.4256624831967197E-2</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="5"/>
-        <v>1.0387643312101911E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.2128312415983599E-2</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.4604565668789809</v>
+        <f t="shared" si="6"/>
+        <v>3.6384937247950798E-2</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>7</v>
@@ -5397,16 +5373,16 @@
         <v>5</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.301744E-2</v>
+        <f t="shared" si="6"/>
+        <v>2.2751999999999998E-2</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="5"/>
-        <v>4.0408499999999995E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.1375999999999999E-2</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="5"/>
-        <v>0.11123595</v>
+        <f t="shared" si="6"/>
+        <v>3.4128000000000006E-2</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>8</v>
@@ -5436,15 +5412,15 @@
         <v>3</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5459,15 +5435,15 @@
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5482,15 +5458,15 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5505,15 +5481,15 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5528,15 +5504,15 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5559,7 +5535,7 @@
         <v>6.9699206969506294E-2</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:F25" si="6">E24</f>
+        <f t="shared" ref="F24:F25" si="7">E24</f>
         <v>6.9699206969506294E-2</v>
       </c>
     </row>
@@ -5578,11 +5554,11 @@
         <v>3.5713643240573516E-2</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="7">D25</f>
+        <f t="shared" ref="E25" si="8">D25</f>
         <v>3.5713643240573516E-2</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.5713643240573516E-2</v>
       </c>
     </row>
@@ -5625,15 +5601,15 @@
       </c>
       <c r="D28" s="4">
         <f>SUM(D29:D38)</f>
-        <v>0.77280925614372808</v>
+        <v>0.95606507934057472</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28:F28" si="8">SUM(E29:E38)</f>
-        <v>0.67906867707914054</v>
+        <f t="shared" ref="E28:F28" si="9">SUM(E29:E38)</f>
+        <v>0.69578123489993871</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="8"/>
-        <v>0.92724863253570988</v>
+        <f t="shared" si="9"/>
+        <v>1.6193108562807803</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
@@ -5650,15 +5626,15 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" ref="D29:F36" si="9">$B29*O3</f>
+        <f t="shared" ref="D29:F36" si="10">$B29*O3</f>
         <v>0</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O29" s="4"/>
@@ -5676,15 +5652,15 @@
         <v>6</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -5699,16 +5675,16 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="9"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="10"/>
+        <v>2.9077951002227136E-2</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="9"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.4538975501113568E-2</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="9"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="10"/>
+        <v>4.361692650334071E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5722,16 +5698,16 @@
         <v>3</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.20846325167037749</v>
+        <f t="shared" si="10"/>
+        <v>0.54575679287304835</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.138975501113585</v>
+        <f t="shared" si="10"/>
+        <v>0.3520249443207108</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="9"/>
-        <v>0.25015590200445303</v>
+        <f t="shared" si="10"/>
+        <v>0.73934966592427231</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5745,15 +5721,15 @@
         <v>3</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -5768,16 +5744,16 @@
         <v>3</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="10"/>
+        <v>0.20805208154873969</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="10"/>
+        <v>0.15603906116155478</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="9"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="10"/>
+        <v>0.66316600993660779</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -5791,15 +5767,15 @@
         <v>3</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -5814,15 +5790,15 @@
         <v>3</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -5845,7 +5821,7 @@
         <v>0.11450584002133177</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" ref="F37:F38" si="10">E37</f>
+        <f t="shared" ref="F37:F38" si="11">E37</f>
         <v>0.11450584002133177</v>
       </c>
       <c r="N37" s="6"/>
@@ -5869,11 +5845,11 @@
         <v>5.8672413895227843E-2</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="11">D38</f>
+        <f t="shared" ref="E38" si="12">D38</f>
         <v>5.8672413895227843E-2</v>
       </c>
       <c r="F38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.8672413895227843E-2</v>
       </c>
       <c r="N38" s="1"/>
@@ -5917,15 +5893,15 @@
       </c>
       <c r="D41" s="4">
         <f>SUM(D42:D51)</f>
-        <v>0.81450190647780363</v>
+        <v>0.89672254036507393</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41:F41" si="12">SUM(E42:E51)</f>
-        <v>0.70686377730185745</v>
+        <f t="shared" ref="E41:F41" si="13">SUM(E42:E51)</f>
+        <v>0.67729749325183197</v>
       </c>
       <c r="F41" s="4">
-        <f t="shared" si="12"/>
-        <v>0.98283883298114394</v>
+        <f t="shared" si="13"/>
+        <v>1.5192484954789991</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5939,15 +5915,15 @@
         <v>4</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" ref="D42:F49" si="13">$B42*O3</f>
+        <f t="shared" ref="D42:F49" si="14">$B42*O3</f>
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5962,15 +5938,15 @@
         <v>6</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F43" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -5985,16 +5961,16 @@
         <v>5</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="13"/>
-        <v>2.9417193763919783E-2</v>
+        <f t="shared" si="14"/>
+        <v>2.9077951002227136E-2</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="13"/>
-        <v>5.1643652561247149E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.4538975501113568E-2</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="13"/>
-        <v>0.14216391982182611</v>
+        <f t="shared" si="14"/>
+        <v>4.361692650334071E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -6008,15 +5984,15 @@
         <v>3</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F45" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -6031,16 +6007,16 @@
         <v>3</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.25015590200445303</v>
+        <f t="shared" si="14"/>
+        <v>0.4864142538975475</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.166770601336302</v>
+        <f t="shared" si="14"/>
+        <v>0.33354120267260401</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.30574610244988704</v>
+        <f t="shared" si="14"/>
+        <v>0.63928730512249099</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -6054,16 +6030,16 @@
         <v>3</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="14"/>
+        <v>0.20805208154873969</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="14"/>
+        <v>0.15603906116155478</v>
       </c>
       <c r="F47" s="4">
-        <f t="shared" si="13"/>
-        <v>0.36175055679287116</v>
+        <f t="shared" si="14"/>
+        <v>0.66316600993660779</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="18" x14ac:dyDescent="0.35">
@@ -6077,15 +6053,15 @@
         <v>3</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -6100,15 +6076,15 @@
         <v>3</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -6131,7 +6107,7 @@
         <v>0.11450584002133177</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" ref="F50:F51" si="14">E50</f>
+        <f t="shared" ref="F50:F51" si="15">E50</f>
         <v>0.11450584002133177</v>
       </c>
     </row>
@@ -6150,11 +6126,11 @@
         <v>5.8672413895227843E-2</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="15">D51</f>
+        <f t="shared" ref="E51" si="16">D51</f>
         <v>5.8672413895227843E-2</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.8672413895227843E-2</v>
       </c>
     </row>
@@ -6242,35 +6218,35 @@
       </c>
       <c r="B2" s="4">
         <f>'2020'!D3</f>
-        <v>7.3373147450400009E-2</v>
+        <v>4.6841402967831812E-2</v>
       </c>
       <c r="C2" s="4">
         <f>'2030'!D3</f>
-        <v>0.35532395073630008</v>
+        <v>7.5579848266936367E-2</v>
       </c>
       <c r="D2" s="4">
         <f>'2040'!D3</f>
-        <v>0.35532395073630008</v>
+        <v>8.0331874654977264E-2</v>
       </c>
       <c r="E2" s="4">
         <f>'2050'!D3</f>
-        <v>0.35532395073630008</v>
+        <v>8.3499892247004548E-2</v>
       </c>
       <c r="F2" s="4">
         <f>'2020'!D16</f>
-        <v>7.3373147450400009E-2</v>
+        <v>4.6841402967831812E-2</v>
       </c>
       <c r="G2" s="4">
         <f>'2030'!D16</f>
-        <v>0.35532395073630008</v>
+        <v>7.5579848266936367E-2</v>
       </c>
       <c r="H2" s="4">
         <f>'2040'!D16</f>
-        <v>0.35532395073630008</v>
+        <v>8.0331874654977264E-2</v>
       </c>
       <c r="I2" s="4">
         <f>'2050'!D16</f>
-        <v>0.35532395073630008</v>
+        <v>8.3499892247004548E-2</v>
       </c>
       <c r="J2" s="4">
         <f>'2020'!D29</f>
@@ -6311,35 +6287,35 @@
       </c>
       <c r="B3" s="4">
         <f>'2020'!D4</f>
-        <v>2.1316738853503187E-2</v>
+        <v>1.3607374905737681E-2</v>
       </c>
       <c r="C3" s="4">
         <f>'2030'!D4</f>
-        <v>0.10323051592356688</v>
+        <v>2.1955860959016391E-2</v>
       </c>
       <c r="D3" s="4">
         <f>'2040'!D4</f>
-        <v>0.10323051592356688</v>
+        <v>2.3336319282786903E-2</v>
       </c>
       <c r="E3" s="4">
         <f>'2050'!D4</f>
-        <v>0.10323051592356688</v>
+        <v>2.4256624831967197E-2</v>
       </c>
       <c r="F3" s="4">
         <f>'2020'!D17</f>
-        <v>2.1316738853503187E-2</v>
+        <v>1.3607374905737681E-2</v>
       </c>
       <c r="G3" s="4">
         <f>'2030'!D17</f>
-        <v>0.10323051592356688</v>
+        <v>2.1955860959016391E-2</v>
       </c>
       <c r="H3" s="4">
         <f>'2040'!D17</f>
-        <v>0.10323051592356688</v>
+        <v>2.3336319282786903E-2</v>
       </c>
       <c r="I3" s="4">
         <f>'2050'!D17</f>
-        <v>0.10323051592356688</v>
+        <v>2.4256624831967197E-2</v>
       </c>
       <c r="J3" s="4">
         <f>'2020'!D30</f>
@@ -6380,67 +6356,67 @@
       </c>
       <c r="B4" s="4">
         <f>'2020'!D5</f>
-        <v>2.2525599999999998E-3</v>
+        <v>7.6960000000000006E-3</v>
       </c>
       <c r="C4" s="4">
         <f>'2030'!D5</f>
-        <v>7.1868799999999997E-3</v>
+        <v>7.6220000000000003E-3</v>
       </c>
       <c r="D4" s="4">
         <f>'2040'!D5</f>
-        <v>7.1868799999999997E-3</v>
+        <v>7.4739999999999989E-3</v>
       </c>
       <c r="E4" s="4">
         <f>'2050'!D5</f>
-        <v>7.1868799999999997E-3</v>
+        <v>7.1040000000000001E-3</v>
       </c>
       <c r="F4" s="4">
         <f>'2020'!D18</f>
-        <v>7.21428E-3</v>
+        <v>2.4648E-2</v>
       </c>
       <c r="G4" s="4">
         <f>'2030'!D18</f>
-        <v>2.301744E-2</v>
+        <v>2.4411000000000002E-2</v>
       </c>
       <c r="H4" s="4">
         <f>'2040'!D18</f>
-        <v>2.301744E-2</v>
+        <v>2.3936999999999996E-2</v>
       </c>
       <c r="I4" s="4">
         <f>'2050'!D18</f>
-        <v>2.301744E-2</v>
+        <v>2.2751999999999998E-2</v>
       </c>
       <c r="J4" s="4">
         <f>'2020'!D31</f>
-        <v>9.2201336302895204E-3</v>
+        <v>3.1501113585746067E-2</v>
       </c>
       <c r="K4" s="4">
         <f>'2030'!D31</f>
-        <v>2.9417193763919783E-2</v>
+        <v>3.11982182628062E-2</v>
       </c>
       <c r="L4" s="4">
         <f>'2040'!D31</f>
-        <v>2.9417193763919783E-2</v>
+        <v>3.0592427616926463E-2</v>
       </c>
       <c r="M4" s="4">
         <f>'2050'!D31</f>
-        <v>2.9417193763919783E-2</v>
+        <v>2.9077951002227136E-2</v>
       </c>
       <c r="N4" s="4">
         <f>'2020'!D44</f>
-        <v>9.2201336302895204E-3</v>
+        <v>3.1501113585746067E-2</v>
       </c>
       <c r="O4" s="4">
         <f>'2030'!D44</f>
-        <v>2.9417193763919783E-2</v>
+        <v>3.11982182628062E-2</v>
       </c>
       <c r="P4" s="4">
         <f>'2040'!D44</f>
-        <v>2.9417193763919783E-2</v>
+        <v>3.0592427616926463E-2</v>
       </c>
       <c r="Q4" s="4">
         <f>'2050'!D44</f>
-        <v>2.9417193763919783E-2</v>
+        <v>2.9077951002227136E-2</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -6481,19 +6457,19 @@
       </c>
       <c r="J5" s="4">
         <f>'2020'!D32</f>
-        <v>0.44472160356347201</v>
+        <v>1.2813541202672538</v>
       </c>
       <c r="K5" s="4">
         <f>'2030'!D32</f>
-        <v>0.34743875278396252</v>
+        <v>0.92696659242761192</v>
       </c>
       <c r="L5" s="4">
         <f>'2040'!D32</f>
-        <v>0.25015590200445303</v>
+        <v>0.73379064587972886</v>
       </c>
       <c r="M5" s="4">
         <f>'2050'!D32</f>
-        <v>0.20846325167037749</v>
+        <v>0.54575679287304835</v>
       </c>
       <c r="N5" s="4">
         <f>'2020'!D45</f>
@@ -6566,19 +6542,19 @@
       </c>
       <c r="N6" s="4">
         <f>'2020'!D46</f>
-        <v>0.41692650334075498</v>
+        <v>0.95615144766146476</v>
       </c>
       <c r="O6" s="4">
         <f>'2030'!D46</f>
-        <v>0.34743875278396252</v>
+        <v>0.79910913140311379</v>
       </c>
       <c r="P6" s="4">
         <f>'2040'!D46</f>
-        <v>0.27795100222717001</v>
+        <v>0.68792873051224579</v>
       </c>
       <c r="Q6" s="4">
         <f>'2050'!D46</f>
-        <v>0.25015590200445303</v>
+        <v>0.4864142538975475</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -6619,35 +6595,35 @@
       </c>
       <c r="J7" s="4">
         <f>'2020'!D34</f>
-        <v>0.76576169265033001</v>
+        <v>0.61115298954942288</v>
       </c>
       <c r="K7" s="4">
         <f>'2030'!D34</f>
-        <v>0.63154040311803683</v>
+        <v>0.32508137741990578</v>
       </c>
       <c r="L7" s="4">
         <f>'2040'!D34</f>
-        <v>0.49686946102449453</v>
+        <v>0.2665667294843227</v>
       </c>
       <c r="M7" s="4">
         <f>'2050'!D34</f>
-        <v>0.36175055679287116</v>
+        <v>0.20805208154873969</v>
       </c>
       <c r="N7" s="4">
         <f>'2020'!D47</f>
-        <v>0.76576169265033001</v>
+        <v>0.61115298954942288</v>
       </c>
       <c r="O7" s="4">
         <f>'2030'!D47</f>
-        <v>0.63154040311803683</v>
+        <v>0.32508137741990578</v>
       </c>
       <c r="P7" s="4">
         <f>'2040'!D47</f>
-        <v>0.49686946102449453</v>
+        <v>0.2665667294843227</v>
       </c>
       <c r="Q7" s="4">
         <f>'2050'!D47</f>
-        <v>0.36175055679287116</v>
+        <v>0.20805208154873969</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18" x14ac:dyDescent="0.35">
@@ -6932,67 +6908,67 @@
       </c>
       <c r="B12" s="4">
         <f>'2020'!E2</f>
-        <v>0.13052289868226805</v>
+        <v>0.11719122170895088</v>
       </c>
       <c r="C12" s="4">
         <f>'2030'!E2</f>
-        <v>0.13737401525426576</v>
+        <v>0.14254880395714026</v>
       </c>
       <c r="D12" s="4">
         <f>'2040'!E2</f>
-        <v>0.14478983896564024</v>
+        <v>0.15295687002442038</v>
       </c>
       <c r="E12" s="4">
         <f>'2050'!E2</f>
-        <v>0.15281691612018172</v>
+        <v>0.1628431087495657</v>
       </c>
       <c r="F12" s="4">
         <f>'2020'!E15</f>
-        <v>0.13330204868226805</v>
+        <v>0.12566722170895089</v>
       </c>
       <c r="G12" s="4">
         <f>'2030'!E15</f>
-        <v>0.14015316525426577</v>
+        <v>0.15094330395714026</v>
       </c>
       <c r="H12" s="4">
         <f>'2040'!E15</f>
-        <v>0.14756898896564025</v>
+        <v>0.16118837002442038</v>
       </c>
       <c r="I12" s="4">
         <f>'2050'!E15</f>
-        <v>0.15559606612018173</v>
+        <v>0.1706671087495657</v>
       </c>
       <c r="J12" s="4">
         <f>'2020'!E28</f>
-        <v>1.2827122790388357</v>
+        <v>1.7664725325937414</v>
       </c>
       <c r="K12" s="4">
         <f>'2030'!E28</f>
-        <v>1.0346684443011696</v>
+        <v>0.93569949912385264</v>
       </c>
       <c r="L12" s="4">
         <f>'2040'!E28</f>
-        <v>0.85659044071659385</v>
+        <v>0.80761332164858168</v>
       </c>
       <c r="M12" s="4">
         <f>'2050'!E28</f>
-        <v>0.67906867707914054</v>
+        <v>0.69578123489993871</v>
       </c>
       <c r="N12" s="4">
         <f>'2020'!E41</f>
-        <v>1.2132245284820433</v>
+        <v>1.3342587241304922</v>
       </c>
       <c r="O12" s="4">
         <f>'2030'!E41</f>
-        <v>1.0346684443011696</v>
+        <v>0.85787321850024512</v>
       </c>
       <c r="P12" s="4">
         <f>'2040'!E41</f>
-        <v>0.88438554093931088</v>
+        <v>0.77954027042363738</v>
       </c>
       <c r="Q12" s="4">
         <f>'2050'!E41</f>
-        <v>0.70686377730185745</v>
+        <v>0.67729749325183197</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -7001,67 +6977,67 @@
       </c>
       <c r="B13" s="4">
         <f>'2020'!F2</f>
-        <v>0.25748312288407949</v>
+        <v>0.18533599958252039</v>
       </c>
       <c r="C13" s="4">
         <f>'2030'!F2</f>
-        <v>2.1700700581164454</v>
+        <v>0.24770651318309297</v>
       </c>
       <c r="D13" s="4">
         <f>'2040'!F2</f>
-        <v>2.1774858818278195</v>
+        <v>0.26409906396218458</v>
       </c>
       <c r="E13" s="4">
         <f>'2050'!F2</f>
-        <v>2.1855129589823612</v>
+        <v>0.27770362582853741</v>
       </c>
       <c r="F13" s="4">
         <f>'2020'!F15</f>
-        <v>0.26460296288407947</v>
+        <v>0.2107639995825204</v>
       </c>
       <c r="G13" s="4">
         <f>'2030'!F15</f>
-        <v>2.2465741081164454</v>
+        <v>0.27289001318309297</v>
       </c>
       <c r="H13" s="4">
         <f>'2040'!F15</f>
-        <v>2.2539899318278196</v>
+        <v>0.28879356396218459</v>
       </c>
       <c r="I13" s="4">
         <f>'2050'!F15</f>
-        <v>2.2620170089823612</v>
+        <v>0.30117562582853746</v>
       </c>
       <c r="J13" s="4">
         <f>'2020'!F28</f>
-        <v>1.4714465329363848</v>
+        <v>3.446778169050817</v>
       </c>
       <c r="K13" s="4">
         <f>'2030'!F28</f>
-        <v>1.2967459498690974</v>
+        <v>2.2774963125554031</v>
       </c>
       <c r="L13" s="4">
         <f>'2040'!F28</f>
-        <v>1.1047703961731636</v>
+        <v>1.9513625078743768</v>
       </c>
       <c r="M13" s="4">
         <f>'2050'!F28</f>
-        <v>0.92724863253570988</v>
+        <v>1.6193108562807803</v>
       </c>
       <c r="N13" s="4">
         <f>'2020'!F41</f>
-        <v>1.4714465329363848</v>
+        <v>2.4155799507880165</v>
       </c>
       <c r="O13" s="4">
         <f>'2030'!F41</f>
-        <v>1.3384386002031727</v>
+        <v>2.0996076711300145</v>
       </c>
       <c r="P13" s="4">
         <f>'2040'!F41</f>
-        <v>1.1603605966185975</v>
+        <v>1.8878507038654684</v>
       </c>
       <c r="Q13" s="4">
         <f>'2050'!F41</f>
-        <v>0.98283883298114394</v>
+        <v>1.5192484954789991</v>
       </c>
     </row>
   </sheetData>
